--- a/04_DESIGN_TABLES/DesignTable_2501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501.xlsx
@@ -2752,7 +2752,7 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -2762,12 +2762,17 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p023-t01: agrees on M@DRIVE, N@DRIVE, Y@REF, D@BORE, D1@DRILL</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2501-06-04-FG</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2943,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -2948,12 +2953,17 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p023-t01: agrees on M@DRIVE, N@DRIVE, Y@REF, D@BORE, D1@DRILL</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2501-06-06-FG</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7088,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>2.64</v>
@@ -7150,10 +7160,14 @@
       </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504)</t>
-        </is>
-      </c>
-      <c r="X72" s="3" t="inlineStr"/>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071)</t>
+        </is>
+      </c>
       <c r="Z72" t="inlineStr">
         <is>
           <t>BUILD</t>

--- a/04_DESIGN_TABLES/DesignTable_2501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1091,7 +1091,7 @@
         <v>0.89</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0.4375</v>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>was "VERIFIED" (vote text in the wrong column); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P661 L 1 Size = 0.78 (table had 0.76 = Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F45D, Q-B-ELBOW answered by the catalog); THDMAJ_A@DRIVE: 0.78 -&gt; 0.4375 (column-shift repair; -04 JIC 7/16-20, gen_straight2 JIC[4]); M / Y / D / D1 = OMi Items!N661 / R661 / S661 / X661 (0.89 equal; the table values 0.44 / 0.17 / 0.19 differ from OMi 0.438 / 0.172 / 0.188 by rounding only and are kept, user 2026-09-25); JIC end MS33656J = Brennan (VERIFIED), NPTF ASME B1.20.3 [batch 15, 2026-10-02, staged for review]</t>
+          <t>was "VERIFIED" (vote text in the wrong column); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P661 L 1 Size = 0.78 (table had 0.76 = Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F45D, Q-B-ELBOW answered by the catalog); THDMAJ_A@DRIVE: 0.78 -&gt; 0.4375 (column-shift repair; -04 JIC 7/16-20, gen_straight2 JIC[4]); M / Y / D / D1 = OMi Items!N661 / R661 / S661 / X661 (0.89 equal; the table values 0.44 / 0.17 / 0.19 differ from OMi 0.438 / 0.172 / 0.188 by rounding only and are kept, user 2026-09-25); JIC end MS33656J = Brennan (VERIFIED), NPTF ASME B1.20.3 [batch 15, 2026-10-02, staged for review]; N@DRIVE: Air-Way 0.76 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51504 - see workbook | 2026-10-02 (batch 15, staged): Air-Way N 0.76 vs MS51504 .780 conflict settled by the OMi-first rule - OMi L 1 Size 0.78 (Items!P661; = Brennan TFA catalog p23 L 0.78); THDMAJ_A held the shifted vote value 0.78 -&gt; repaired to 0.4375 (-04 JIC); Q-CONFLICT-2501-04-02-FG not needed (impact F45D)</t>
+          <t>CONFLICT vs MS51504 - see workbook | 2026-10-02 (batch 15, staged): Air-Way N 0.76 vs MS51504 .780 conflict settled by the OMi-first rule - OMi L 1 Size 0.78 (Items!P661; = Brennan TFA catalog p23 L 0.78); THDMAJ_A held the shifted vote value 0.78 -&gt; repaired to 0.4375 (-04 JIC); Q-CONFLICT-2501-04-02-FG not needed (impact F45D) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.76</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>2.64</v>
@@ -7160,12 +7160,12 @@
       </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19]</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19]; M@DRIVE: Air-Way 2.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071) | 2026-10-20 Air-Way first: M@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.3</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -7794,7 +7794,7 @@
         <v>1.5</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>1.875</v>
+        <v>1.81</v>
       </c>
       <c r="S79" s="3" t="inlineStr">
         <is>
@@ -7818,10 +7818,14 @@
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="X79" s="3" t="inlineStr"/>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: Y@REF OMi/Brennan 1.875 -&gt; Air-Way 1.81</t>
+        </is>
+      </c>
       <c r="Z79" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -7885,7 +7889,7 @@
         <v>1.78</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>1.938</v>
+        <v>1.86</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>2.5</v>
@@ -7912,12 +7916,12 @@
       </c>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3)</t>
+          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3); D1@DRILL: Air-Way 1.86 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.938) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50</t>
+          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50 | 2026-10-20 Air-Way first: D1@DRILL OMi/Brennan 1.938 -&gt; Air-Way 1.86</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
